--- a/databases/tabela_contingencia_inicio.xlsx
+++ b/databases/tabela_contingencia_inicio.xlsx
@@ -382,14 +382,20 @@
           <t>Highest rates</t>
         </is>
       </c>
-      <c r="B2">
-        <v>619</v>
-      </c>
-      <c r="C2">
-        <v>1656</v>
-      </c>
-      <c r="D2">
-        <v>189</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>42 (0.8%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>156 (2.8%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>697 (12.5%)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -398,14 +404,20 @@
           <t>Intermediary rates</t>
         </is>
       </c>
-      <c r="B3">
-        <v>519</v>
-      </c>
-      <c r="C3">
-        <v>1528</v>
-      </c>
-      <c r="D3">
-        <v>163</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>163 (2.9%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>519 (9.3%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1528 (27.4%)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -414,14 +426,20 @@
           <t>Lowest rates</t>
         </is>
       </c>
-      <c r="B4">
-        <v>156</v>
-      </c>
-      <c r="C4">
-        <v>697</v>
-      </c>
-      <c r="D4">
-        <v>42</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>189 (3.4%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>619 (11.1%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1656 (29.7%)</t>
+        </is>
       </c>
     </row>
   </sheetData>
